--- a/LEARNING/Articulation and Project Mgmt/New Microsoft Excel Worksheet.xlsx
+++ b/LEARNING/Articulation and Project Mgmt/New Microsoft Excel Worksheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/LEARNING/Articulation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/LEARNING/Articulation and Project Mgmt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B11CEB4B-2024-4706-AA08-63F97F8CBBE2}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4066D8F5-69B8-4890-B416-338D5CBEDD9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>I think maybe we should proceed with</t>
   </si>
@@ -114,6 +114,21 @@
   </si>
   <si>
     <t>Slow down, then finish the thought</t>
+  </si>
+  <si>
+    <t>Where we scored low is….</t>
+  </si>
+  <si>
+    <t>please walk us through….</t>
+  </si>
+  <si>
+    <t>you guys figure it out whatever works for it…</t>
+  </si>
+  <si>
+    <t>what is the point of having multiple traces</t>
+  </si>
+  <si>
+    <t>Our recommendation is that, it has to be tied back to this…</t>
   </si>
 </sst>
 </file>
@@ -443,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -554,6 +569,31 @@
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/LEARNING/Articulation and Project Mgmt/New Microsoft Excel Worksheet.xlsx
+++ b/LEARNING/Articulation and Project Mgmt/New Microsoft Excel Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/LEARNING/Articulation and Project Mgmt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4066D8F5-69B8-4890-B416-338D5CBEDD9E}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A0A7EA8-51A6-4C34-A877-88FFE91C35E4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>I think maybe we should proceed with</t>
   </si>
@@ -129,19 +129,137 @@
   </si>
   <si>
     <t>Our recommendation is that, it has to be tied back to this…</t>
+  </si>
+  <si>
+    <t>I will do it</t>
+  </si>
+  <si>
+    <t>I will take this forward</t>
+  </si>
+  <si>
+    <t>I will handle it</t>
+  </si>
+  <si>
+    <t>Let me take ownership for this</t>
+  </si>
+  <si>
+    <t>Leave it to me</t>
+  </si>
+  <si>
+    <t>I will take this from here</t>
+  </si>
+  <si>
+    <t>I forgot</t>
+  </si>
+  <si>
+    <t>That slipped off from my radar</t>
+  </si>
+  <si>
+    <t>I didn't do it yet</t>
+  </si>
+  <si>
+    <t>this is still pending from my end</t>
+  </si>
+  <si>
+    <t>I will check</t>
+  </si>
+  <si>
+    <t>I will look into this</t>
+  </si>
+  <si>
+    <t>I will ask them</t>
+  </si>
+  <si>
+    <t>I will follow up with them</t>
+  </si>
+  <si>
+    <t>I will tell you</t>
+  </si>
+  <si>
+    <t>I will keep you posted</t>
+  </si>
+  <si>
+    <t>I don’t know</t>
+  </si>
+  <si>
+    <t>let me circle back with an update</t>
+  </si>
+  <si>
+    <t>this will help us</t>
+  </si>
+  <si>
+    <t>this will enable us to move forward</t>
+  </si>
+  <si>
+    <t>This is important</t>
+  </si>
+  <si>
+    <t>This is key priority</t>
+  </si>
+  <si>
+    <t>This made a big difference</t>
+  </si>
+  <si>
+    <t>This made a significant impact</t>
+  </si>
+  <si>
+    <t>Can we connect now</t>
+  </si>
+  <si>
+    <t>Would you be available for a quick discussion today</t>
+  </si>
+  <si>
+    <t>Would it be possible to connect sometime today</t>
+  </si>
+  <si>
+    <t>I am happy to jump on quick call if that works for you</t>
+  </si>
+  <si>
+    <t>Would you be available for a breif discussion later today</t>
+  </si>
+  <si>
+    <t>Let me know your convenient time today</t>
+  </si>
+  <si>
+    <t>Shall we catch up briefly today</t>
+  </si>
+  <si>
+    <t>please wait for 2 days. I will check it and update you for closure</t>
+  </si>
+  <si>
+    <t>I appreciated your help in closing the data piece
+Suggest to just allow us 2 more days, until myself and Madhavan sit and cross check once on a final basis, which is planned for tomorrow </t>
+  </si>
+  <si>
+    <t>there are still a substantial number of items that remain unclassified.</t>
+  </si>
+  <si>
+    <t>there are few items to be categorized</t>
+  </si>
+  <si>
+    <t>It would also be helpful if you could direct us to the appropriate owners or subject matter experts who can assist with this exercise.</t>
+  </si>
+  <si>
+    <t>It will be helpful if we are provided with SPOC for the respective teams</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -164,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -177,6 +295,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,11 +579,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="63.7109375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -572,28 +693,181 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/LEARNING/Articulation and Project Mgmt/New Microsoft Excel Worksheet.xlsx
+++ b/LEARNING/Articulation and Project Mgmt/New Microsoft Excel Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/LEARNING/Articulation and Project Mgmt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A0A7EA8-51A6-4C34-A877-88FFE91C35E4}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7745CAE-AFF2-4917-8156-2B0A4692AFCF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>I think maybe we should proceed with</t>
   </si>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>It will be helpful if we are provided with SPOC for the respective teams</t>
+  </si>
+  <si>
+    <t>on Project Standpoint, what are the pending items</t>
+  </si>
+  <si>
+    <t>what is the pending items among project list</t>
   </si>
 </sst>
 </file>
@@ -579,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -868,6 +874,14 @@
       </c>
       <c r="B40" s="3" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
